--- a/reports/history/build-5/Failed_Test_Cases.xlsx
+++ b/reports/history/build-5/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,100 +34,97 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AZ_003</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Authorization Verification - Case 3</t>
+    <t>TC_PROF_019</t>
+  </si>
+  <si>
+    <t>Profile Management</t>
+  </si>
+  <si>
+    <t>Profile Management Verification - Case 19</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 108</t>
+  </si>
+  <si>
+    <t>TC_FORM_016</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Forms Verification - Case 16</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 175</t>
+  </si>
+  <si>
+    <t>TC_CRUD_003</t>
+  </si>
+  <si>
+    <t>CRUD Operations</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 3</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 42</t>
-  </si>
-  <si>
-    <t>TC_NAV_025</t>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 25</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 134</t>
-  </si>
-  <si>
-    <t>TC_FORM_032</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 32</t>
+    <t>AssertionError: State mismatch on scenario index 202</t>
+  </si>
+  <si>
+    <t>TC_CRUD_019</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 19</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 218</t>
+  </si>
+  <si>
+    <t>TC_SRCH_009</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 9</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 248</t>
+  </si>
+  <si>
+    <t>TC_FILT_009</t>
+  </si>
+  <si>
+    <t>Filters</t>
+  </si>
+  <si>
+    <t>Filters Verification - Case 9</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 268</t>
+  </si>
+  <si>
+    <t>TC_ACC_014</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 14</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 191</t>
-  </si>
-  <si>
-    <t>TC_NOTIF_014</t>
-  </si>
-  <si>
-    <t>Notifications</t>
-  </si>
-  <si>
-    <t>Notifications Verification - Case 14</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 373</t>
-  </si>
-  <si>
-    <t>TC_ACC_010</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Accessibility Verification - Case 10</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 419</t>
-  </si>
-  <si>
-    <t>TC_PERF_014</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests Verification - Case 14</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 453</t>
-  </si>
-  <si>
-    <t>TC_REGR_038</t>
-  </si>
-  <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 38</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 497</t>
+    <t>AssertionError: State mismatch on scenario index 423</t>
   </si>
 </sst>
 </file>
@@ -521,8 +518,8 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -569,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>165</v>
+        <v>251</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -586,131 +583,131 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>262</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>295</v>
+        <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
